--- a/DataSheets/COPYcore40MetadataAndLin2014_2.xlsx
+++ b/DataSheets/COPYcore40MetadataAndLin2014_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/ExtDrive850X/MATLAB/nSRdist_code/DataSheets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samnewall/Documents/Research/nSRdist_code/DataSheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4571C8B7-D7E2-AF48-9273-404EE036E4F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D4D5BB-F241-B643-9E2F-8A5978273EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38300" yWindow="1260" windowWidth="21600" windowHeight="21120" xr2:uid="{241646B2-7963-A24D-AB44-A51AF08C0A54}"/>
+    <workbookView xWindow="10360" yWindow="600" windowWidth="21600" windowHeight="21000" xr2:uid="{241646B2-7963-A24D-AB44-A51AF08C0A54}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
